--- a/工具类教程API/IDEA快捷键 Excle版本.xlsx
+++ b/工具类教程API/IDEA快捷键 Excle版本.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gouwe\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD1BD055-9143-466D-8391-06CB3FD48457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2844DB47-3823-4A27-AE69-9A2C28CB8215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{35698B27-D6DB-4706-99A9-A44C881F0DA1}"/>
   </bookViews>
@@ -36,6 +36,57 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>苟文勇</author>
+  </authors>
+  <commentList>
+    <comment ref="H22" authorId="0" shapeId="0" xr:uid="{A68C6EB4-A361-4334-8451-0EB76DDA699D}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+显示当前类的继承结构，包括父类和子类（接口同样适用）。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H23" authorId="0" shapeId="0" xr:uid="{FC8E1B50-8225-49E8-B2B4-63AA4459D554}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>显示当前方法在继承层次中的实现或重写关系。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H24" authorId="0" shapeId="0" xr:uid="{115191BB-F167-4C23-8D75-6D8BE2A72B71}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve"> 查看某个方法或成员变量的调用关系，谁调用了它、它又调用了谁。</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="255">
   <si>
@@ -830,7 +881,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -894,8 +945,21 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -905,6 +969,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -923,7 +999,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -960,8 +1036,26 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1481,7 +1575,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{134CF0DD-53AE-4E72-93C2-2C541A5ED55D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{134CF0DD-53AE-4E72-93C2-2C541A5ED55D}">
   <dimension ref="A1:H53"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1497,14 +1591,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="E1" s="12"/>
-      <c r="G1" s="12" t="s">
+      <c r="E1" s="15"/>
+      <c r="G1" s="15" t="s">
         <v>236</v>
       </c>
-      <c r="H1" s="12"/>
+      <c r="H1" s="15"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D2" s="2" t="s">
@@ -1549,10 +1643,10 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="18" t="s">
         <v>73</v>
       </c>
       <c r="G5" s="2" t="s">
@@ -1563,14 +1657,14 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="D6" s="2" t="s">
+      <c r="B6" s="15"/>
+      <c r="D6" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="18" t="s">
         <v>75</v>
       </c>
       <c r="G6" s="2" t="s">
@@ -1633,10 +1727,10 @@
       <c r="E9" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="17" t="s">
         <v>167</v>
       </c>
     </row>
@@ -1789,10 +1883,10 @@
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="B18" s="12"/>
+      <c r="B18" s="15"/>
       <c r="D18" s="2" t="s">
         <v>96</v>
       </c>
@@ -1859,10 +1953,10 @@
       <c r="E21" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="H21" s="13" t="s">
         <v>187</v>
       </c>
     </row>
@@ -1879,10 +1973,10 @@
       <c r="E22" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="G22" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="H22" s="13" t="s">
         <v>189</v>
       </c>
     </row>
@@ -1899,10 +1993,10 @@
       <c r="E23" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="G23" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="H23" s="13" t="s">
         <v>191</v>
       </c>
     </row>
@@ -1919,10 +2013,10 @@
       <c r="E24" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G24" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="H24" s="5" t="s">
+      <c r="H24" s="13" t="s">
         <v>193</v>
       </c>
     </row>
@@ -2001,10 +2095,10 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
+      <c r="A29" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="B29" s="12"/>
+      <c r="B29" s="15"/>
       <c r="D29" s="2" t="s">
         <v>117</v>
       </c>
@@ -2087,10 +2181,10 @@
       <c r="E33" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="G33" s="12" t="s">
+      <c r="G33" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="H33" s="12"/>
+      <c r="H33" s="15"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
@@ -2167,10 +2261,10 @@
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="12" t="s">
+      <c r="A38" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="B38" s="12"/>
+      <c r="B38" s="15"/>
       <c r="G38" s="2" t="s">
         <v>218</v>
       </c>
@@ -2185,10 +2279,10 @@
       <c r="B39" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D39" s="12" t="s">
+      <c r="D39" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="E39" s="12"/>
+      <c r="E39" s="15"/>
       <c r="G39" s="2"/>
       <c r="H39" s="5"/>
     </row>
@@ -2205,10 +2299,10 @@
       <c r="E40" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="G40" s="12" t="s">
+      <c r="G40" s="15" t="s">
         <v>238</v>
       </c>
-      <c r="H40" s="12"/>
+      <c r="H40" s="15"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
@@ -2223,10 +2317,10 @@
       <c r="E41" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="G41" s="4" t="s">
+      <c r="G41" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="H41" s="5" t="s">
+      <c r="H41" s="13" t="s">
         <v>205</v>
       </c>
     </row>
@@ -2243,10 +2337,10 @@
       <c r="E42" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="G42" s="4" t="s">
+      <c r="G42" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="H42" s="5" t="s">
+      <c r="H42" s="13" t="s">
         <v>207</v>
       </c>
     </row>
@@ -2263,10 +2357,10 @@
       <c r="E43" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G43" s="4" t="s">
+      <c r="G43" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="H43" s="5" t="s">
+      <c r="H43" s="13" t="s">
         <v>209</v>
       </c>
     </row>
@@ -2299,10 +2393,10 @@
       <c r="E45" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="G45" s="12" t="s">
+      <c r="G45" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="H45" s="12"/>
+      <c r="H45" s="15"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
@@ -2389,10 +2483,10 @@
       <c r="E51" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="G51" s="12" t="s">
+      <c r="G51" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="H51" s="12"/>
+      <c r="H51" s="15"/>
     </row>
     <row r="52" spans="4:8" x14ac:dyDescent="0.25">
       <c r="G52" s="10" t="s">
@@ -2428,6 +2522,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
